--- a/cve/webid-cve.xlsx
+++ b/cve/webid-cve.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['username']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -532,11 +532,11 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVE-2008-7118</t>
+          <t>CVE-2008-7119</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -551,97 +551,97 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['item.php']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['id']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>WeBid auction script 0.5.4 stores sensitive information under the web root with insufficient access control, which allows remote attackers to obtain SQL query logs via a direct request for logs/cron.log.</t>
+          <t>SQL injection vulnerability in item.php in WeBid auction script 0.5.4 allows remote attackers to execute arbitrary SQL commands via the id parameter.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVE-2008-7119</t>
+          <t>CVE-2006-3362</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>File Inclusion</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['0.5.4']</t>
+          <t>['1.4.0', '1.4.0', '1.0.0', '0.5.4']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['item.php']</t>
+          <t>['connector.php']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['id']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SQL injection vulnerability in item.php in WeBid auction script 0.5.4 allows remote attackers to execute arbitrary SQL commands via the id parameter.</t>
+          <t>Unrestricted file upload vulnerability in connectors/php/connector.php in FCKeditor mcpuk file manager, as used in (1) Geeklog 1.4.0 through 1.4.0sr3, (2) toendaCMS 1.0.0 Shizouka Stable and earlier, (3) WeBid 0.5.4, and possibly other products, when installed on Apache with mod_mime, allows remote attackers to upload and execute arbitrary PHP code via a filename with a .php extension and a trailing extension that is allowed, such as .zip.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVE-2006-3362</t>
+          <t>CVE-2008-1470</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>File Inclusion</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['1.4.0', '1.4.0', '1.0.0', '0.5.4']</t>
+          <t>['5.3']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['connector.php']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['postdata']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Unrestricted file upload vulnerability in connectors/php/connector.php in FCKeditor mcpuk file manager, as used in (1) Geeklog 1.4.0 through 1.4.0sr3, (2) toendaCMS 1.0.0 Shizouka Stable and earlier, (3) WeBid 0.5.4, and possibly other products, when installed on Apache with mod_mime, allows remote attackers to upload and execute arbitrary PHP code via a filename with a .php extension and a trailing extension that is allowed, such as .zip.</t>
+          <t>Incomplete blacklist vulnerability in IISWebAgentIF.dll in the WebID RSA Authentication Agent 5.3, and possibly earlier, allows remote attackers to conduct cross-site scripting (XSS) attacks via the postdata parameter, due to an incomplete fix for CVE-2005-1118.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVE-2008-1470</t>
+          <t>CVE-2008-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['5.3']</t>
+          <t>['5.3.0', '5.3.3']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -661,22 +661,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['postdata']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Incomplete blacklist vulnerability in IISWebAgentIF.dll in the WebID RSA Authentication Agent 5.3, and possibly earlier, allows remote attackers to conduct cross-site scripting (XSS) attacks via the postdata parameter, due to an incomplete fix for CVE-2005-1118.</t>
+          <t>Cross-site scripting (XSS) vulnerability in WebID/IISWebAgentIF.dll in RSA Authentication Agent 5.3.0.258, and other versions before 5.3.3.378, allows remote attackers to inject arbitrary web script or HTML via a URL-encoded postdata parameter.  NOTE: this is different than CVE-2005-1118, but it might be the same as CVE-2008-1470.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVE-2008-2026</t>
+          <t>CVE-2014-5101</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -686,32 +686,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['5.3.0', '5.3.3']</t>
+          <t>['1.1.1']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['register.php', 'user_login.php']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['postdata']</t>
+          <t>['username']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cross-site scripting (XSS) vulnerability in WebID/IISWebAgentIF.dll in RSA Authentication Agent 5.3.0.258, and other versions before 5.3.3.378, allows remote attackers to inject arbitrary web script or HTML via a URL-encoded postdata parameter.  NOTE: this is different than CVE-2005-1118, but it might be the same as CVE-2008-1470.</t>
+          <t>Multiple cross-site scripting (XSS) vulnerabilities in WeBid 1.1.1 allow remote attackers to inject arbitrary web script or HTML via the (1) TPL_name, (2) TPL_nick, (3) TPL_email, (4) TPL_year, (5) TPL_address, (6) TPL_city, (7) TPL_prov, (8) TPL_zip, (9) TPL_phone, (10) TPL_pp_email, (11) TPL_authnet_id, (12) TPL_authnet_pass, (13) TPL_worldpay_id, (14) TPL_toocheckout_id, or (15) TPL_moneybookers_email in a first action to register.php or the (16) username parameter in a login action to user_login.php.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVE-2014-5101</t>
+          <t>CVE-2010-4873</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -721,72 +721,72 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['1.1.1']</t>
+          <t>['0.8.5']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['register.php', 'user_login.php']</t>
+          <t>['confirm.php']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['username']</t>
+          <t>['id']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Multiple cross-site scripting (XSS) vulnerabilities in WeBid 1.1.1 allow remote attackers to inject arbitrary web script or HTML via the (1) TPL_name, (2) TPL_nick, (3) TPL_email, (4) TPL_year, (5) TPL_address, (6) TPL_city, (7) TPL_prov, (8) TPL_zip, (9) TPL_phone, (10) TPL_pp_email, (11) TPL_authnet_id, (12) TPL_authnet_pass, (13) TPL_worldpay_id, (14) TPL_toocheckout_id, or (15) TPL_moneybookers_email in a first action to register.php or the (16) username parameter in a login action to user_login.php.</t>
+          <t>Cross-site scripting (XSS) vulnerability in confirm.php in WeBid 0.8.5 P1 allows remote attackers to inject arbitrary web script or HTML via the id parameter.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVE-2010-4873</t>
+          <t>CVE-2018-1000867</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>SQL Injection</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['0.8.5']</t>
+          <t>['1.2.2']</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['confirm.php']</t>
+          <t>['yourauctions']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['id']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cross-site scripting (XSS) vulnerability in confirm.php in WeBid 0.8.5 P1 allows remote attackers to inject arbitrary web script or HTML via the id parameter.</t>
+          <t>WeBid version up to current version 1.2.2 contains a SQL Injection vulnerability in All five yourauctions*.php scripts that can result in Database Read via Blind SQL Injection. This attack appear to be exploitable via HTTP Request. This vulnerability appears to have been fixed in after commit 256a5f9d3eafbc477dcf77c7682446cc4b449c7f.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVE-2018-1000867</t>
+          <t>CVE-2018-1000868</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -796,27 +796,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>['user_login.php', 'register.php']</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>WeBid version up to current version 1.2.2 contains a SQL Injection vulnerability in All five yourauctions*.php scripts that can result in Database Read via Blind SQL Injection. This attack appear to be exploitable via HTTP Request. This vulnerability appears to have been fixed in after commit 256a5f9d3eafbc477dcf77c7682446cc4b449c7f.</t>
+          <t>WeBid version up to current version 1.2.2 contains a Cross Site Scripting (XSS) vulnerability in user_login.php, register.php that can result in Javascript execution in the user's browser, injection of malicious markup into the page. This attack appear to be exploitable via The victim user must click a malicous link. This vulnerability appears to have been fixed in after commit 256a5f9d3eafbc477dcf77c7682446cc4b449c7f.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVE-2018-1000868</t>
+          <t>CVE-2019-11592</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -831,87 +831,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['user_login.php', 'register.php']</t>
+          <t>['deletenews.php', 'editbannersuser.php', 'editfaqscategory.php', 'excludeuser.php', 'edituser.php']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['id', 'offset']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>WeBid version up to current version 1.2.2 contains a Cross Site Scripting (XSS) vulnerability in user_login.php, register.php that can result in Javascript execution in the user's browser, injection of malicious markup into the page. This attack appear to be exploitable via The victim user must click a malicous link. This vulnerability appears to have been fixed in after commit 256a5f9d3eafbc477dcf77c7682446cc4b449c7f.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CVE-2019-11592</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>['1.2.2']</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>['deletenews.php', 'editbannersuser.php', 'editfaqscategory.php', 'excludeuser.php', 'edituser.php']</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>['id', 'offset']</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>WeBid 1.2.2 has reflected XSS via the id parameter to admin/deletenews.php, admin/editbannersuser.php, admin/editfaqscategory.php, or admin/excludeuser.php, or the offset parameter to admin/edituser.php.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CVE-2023-2164</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>['16.0.8', '16.1.3', '16.2.2', '15.9', '16.1', '16.2']</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>An issue has been discovered in GitLab affecting all versions starting from 15.9 before 16.0.8, all versions starting from 16.1 before 16.1.3, all versions starting from 16.2 before 16.2.2. It was possible for an attacker to trigger a stored XSS vulnerability via user interaction with a crafted URL in the WebIDE beta.</t>
         </is>
       </c>
     </row>

--- a/cve/webid-cve.xlsx
+++ b/cve/webid-cve.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,46 +462,46 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVE-2008-7116</t>
+          <t>CVE-2006-3362</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>File Inclusion</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['0.5.4']</t>
+          <t>['1.4.0', '1.4.0', '1.0.0', '0.5.4']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['connector.php']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['username']</t>
+          <t>['toendaCMS', 'WeBid', 'Geeklog']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SQL injection vulnerability in the admin panel (admin/) in WeBid auction script 0.5.4 allows remote attackers to execute arbitrary SQL commands via the username.</t>
+          <t>Unrestricted file upload vulnerability in connectors/php/connector.php in FCKeditor mcpuk file manager, as used in (1) Geeklog 1.4.0 through 1.4.0sr3, (2) toendaCMS 1.0.0 Shizouka Stable and earlier, (3) WeBid 0.5.4, and possibly other products, when installed on Apache with mod_mime, allows remote attackers to upload and execute arbitrary PHP code via a filename with a .php extension and a trailing extension that is allowed, such as .zip.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVE-2008-7117</t>
+          <t>CVE-2008-1470</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -511,137 +511,137 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['0.5.4']</t>
+          <t>['5.3']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['eledicss.php']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['file']</t>
+          <t>['postdata']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>eledicss.php in WeBid auction script 0.5.4 allows remote attackers to modify arbitrary cascading style sheets (CSS) files via a certain request with the file parameter set to style.css.  NOTE: this can probably be leveraged for cross-site scripting (XSS) attacks.</t>
+          <t>Incomplete blacklist vulnerability in IISWebAgentIF.dll in the WebID RSA Authentication Agent 5.3, and possibly earlier, allows remote attackers to conduct cross-site scripting (XSS) attacks via the postdata parameter, due to an incomplete fix for CVE-2005-1118.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVE-2008-7119</t>
+          <t>CVE-2008-2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['0.5.4']</t>
+          <t>['5.3.0', '5.3.3']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['item.php']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['id']</t>
+          <t>['postdata']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SQL injection vulnerability in item.php in WeBid auction script 0.5.4 allows remote attackers to execute arbitrary SQL commands via the id parameter.</t>
+          <t>Cross-site scripting (XSS) vulnerability in WebID/IISWebAgentIF.dll in RSA Authentication Agent 5.3.0.258, and other versions before 5.3.3.378, allows remote attackers to inject arbitrary web script or HTML via a URL-encoded postdata parameter.  NOTE: this is different than CVE-2005-1118, but it might be the same as CVE-2008-1470.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVE-2006-3362</t>
+          <t>CVE-2008-7117</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>File Inclusion</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['1.4.0', '1.4.0', '1.0.0', '0.5.4']</t>
+          <t>['0.5.4']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['connector.php']</t>
+          <t>['eledicss.php']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['file']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Unrestricted file upload vulnerability in connectors/php/connector.php in FCKeditor mcpuk file manager, as used in (1) Geeklog 1.4.0 through 1.4.0sr3, (2) toendaCMS 1.0.0 Shizouka Stable and earlier, (3) WeBid 0.5.4, and possibly other products, when installed on Apache with mod_mime, allows remote attackers to upload and execute arbitrary PHP code via a filename with a .php extension and a trailing extension that is allowed, such as .zip.</t>
+          <t>eledicss.php in WeBid auction script 0.5.4 allows remote attackers to modify arbitrary cascading style sheets (CSS) files via a certain request with the file parameter set to style.css.  NOTE: this can probably be leveraged for cross-site scripting (XSS) attacks.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVE-2008-1470</t>
+          <t>CVE-2008-7119</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>SQL Injection</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['5.3']</t>
+          <t>['0.5.4']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['item.php']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['postdata']</t>
+          <t>['id']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Incomplete blacklist vulnerability in IISWebAgentIF.dll in the WebID RSA Authentication Agent 5.3, and possibly earlier, allows remote attackers to conduct cross-site scripting (XSS) attacks via the postdata parameter, due to an incomplete fix for CVE-2005-1118.</t>
+          <t>SQL injection vulnerability in item.php in WeBid auction script 0.5.4 allows remote attackers to execute arbitrary SQL commands via the id parameter.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVE-2008-2026</t>
+          <t>CVE-2010-4873</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -651,28 +651,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['5.3.0', '5.3.3']</t>
+          <t>['0.8.5']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['confirm.php']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['postdata']</t>
+          <t>['id']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cross-site scripting (XSS) vulnerability in WebID/IISWebAgentIF.dll in RSA Authentication Agent 5.3.0.258, and other versions before 5.3.3.378, allows remote attackers to inject arbitrary web script or HTML via a URL-encoded postdata parameter.  NOTE: this is different than CVE-2005-1118, but it might be the same as CVE-2008-1470.</t>
+          <t>Cross-site scripting (XSS) vulnerability in confirm.php in WeBid 0.8.5 P1 allows remote attackers to inject arbitrary web script or HTML via the id parameter.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['username']</t>
+          <t>['TPL_email', 'TPL_pp_email', 'TPL_year', 'TPL_address', 'TPL_authnet_id', 'TPL_phone', 'TPL_moneybookers_email', 'username', 'TPL_nick', 'TPL_toocheckout_id', 'TPL_zip', 'TPL_authnet_pass', 'TPL_worldpay_id', 'TPL_city', 'TPL_prov', 'TPL_name']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -707,11 +707,11 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVE-2010-4873</t>
+          <t>CVE-2019-11592</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -721,125 +721,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['0.8.5']</t>
+          <t>['1.2.2']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['confirm.php']</t>
+          <t>['deletenews.php', 'editbannersuser.php', 'editfaqscategory.php', 'excludeuser.php', 'edituser.php']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['id']</t>
+          <t>['id', 'offset']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t>Cross-site scripting (XSS) vulnerability in confirm.php in WeBid 0.8.5 P1 allows remote attackers to inject arbitrary web script or HTML via the id parameter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CVE-2018-1000867</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SQL Injection</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>['1.2.2']</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>['yourauctions']</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>WeBid version up to current version 1.2.2 contains a SQL Injection vulnerability in All five yourauctions*.php scripts that can result in Database Read via Blind SQL Injection. This attack appear to be exploitable via HTTP Request. This vulnerability appears to have been fixed in after commit 256a5f9d3eafbc477dcf77c7682446cc4b449c7f.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CVE-2018-1000868</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>['1.2.2']</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>['user_login.php', 'register.php']</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>WeBid version up to current version 1.2.2 contains a Cross Site Scripting (XSS) vulnerability in user_login.php, register.php that can result in Javascript execution in the user's browser, injection of malicious markup into the page. This attack appear to be exploitable via The victim user must click a malicous link. This vulnerability appears to have been fixed in after commit 256a5f9d3eafbc477dcf77c7682446cc4b449c7f.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CVE-2019-11592</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>['1.2.2']</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>['deletenews.php', 'editbannersuser.php', 'editfaqscategory.php', 'excludeuser.php', 'edituser.php']</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>['id', 'offset']</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>WeBid 1.2.2 has reflected XSS via the id parameter to admin/deletenews.php, admin/editbannersuser.php, admin/editfaqscategory.php, or admin/excludeuser.php, or the offset parameter to admin/edituser.php.</t>
         </is>
